--- a/excel/Actor.xlsx
+++ b/excel/Actor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t/>
   </si>
@@ -271,6 +271,15 @@
   </si>
   <si>
     <t>effects/chest/ChestActorLarge</t>
+  </si>
+  <si>
+    <t>张角</t>
+  </si>
+  <si>
+    <t>fishes/ZhangJiao/ZhangJiaoActor</t>
+  </si>
+  <si>
+    <t>fishes/Avatars/zhangjiao</t>
   </si>
 </sst>
 </file>
@@ -280,7 +289,7 @@
   <numFmts count="1">
     <numFmt numFmtId="300" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -311,8 +320,11 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,6 +334,7 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill/>
   </fills>
   <borders count="3">
     <border>
@@ -336,21 +349,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs>
-    <xf numFmtId="300" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -363,13 +376,19 @@
     <xf fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="2" borderId="2" xfId="0" applyAlignment="true">
+    <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf fontId="4" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="false" shrinkToFit="false"/>
+    </xf>
+    <xf fontId="4" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -665,27 +684,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="XFE17"/>
+  <dimension ref="AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="6" bestFit="true" customWidth="true"/>
-    <col min="2" max="2" width="11.625" style="6" bestFit="true" customWidth="true"/>
-    <col min="3" max="3" width="37.125" style="6" bestFit="true" customWidth="true"/>
-    <col min="4" max="4" width="30.5" style="6" customWidth="true"/>
-    <col min="5" max="5" width="7.5" style="6" bestFit="true" customWidth="true"/>
-    <col min="6" max="6" width="17.25" style="6" bestFit="true" customWidth="true"/>
-    <col min="7" max="7" width="17.25" style="6" customWidth="true"/>
-    <col min="8" max="8" width="8.5" style="6" bestFit="true" customWidth="true"/>
-    <col min="9" max="9" width="7.5" style="6" bestFit="true" customWidth="true"/>
-    <col min="10" max="10" width="7.5" style="6" customWidth="true"/>
-    <col min="11" max="11" width="7.5" style="6" bestFit="true" customWidth="true"/>
-    <col min="12" max="12" width="9" style="6"/>
-    <col min="13" max="13" width="11.625" style="6" bestFit="true" customWidth="true"/>
-    <col min="14" max="14" width="28.25" style="6" bestFit="true" customWidth="true"/>
-    <col min="15" max="15" width="10" style="6" bestFit="true" customWidth="true"/>
-    <col min="16" max="16" width="15.625" style="6" bestFit="true" customWidth="true"/>
-    <col min="17" max="17" width="11.625" style="6" bestFit="true" customWidth="true"/>
-    <col min="18" max="26" width="9" style="6"/>
+    <col min="1" max="1" width="7.5" style="8" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="11.625" style="8" bestFit="true" customWidth="true"/>
+    <col min="3" max="3" width="37.125" style="8" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="30.5" style="8" customWidth="true"/>
+    <col min="5" max="5" width="7.5" style="8" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="17.25" style="8" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="17.25" style="8" customWidth="true"/>
+    <col min="8" max="8" width="8.5" style="8" bestFit="true" customWidth="true"/>
+    <col min="9" max="9" width="7.5" style="8" bestFit="true" customWidth="true"/>
+    <col min="10" max="10" width="7.5" style="8" customWidth="true"/>
+    <col min="11" max="11" width="7.5" style="8" bestFit="true" customWidth="true"/>
+    <col min="12" max="12" width="9" style="8"/>
+    <col min="13" max="13" width="11.625" style="8" bestFit="true" customWidth="true"/>
+    <col min="14" max="14" width="28.25" style="8" bestFit="true" customWidth="true"/>
+    <col min="15" max="15" width="10" style="8" bestFit="true" customWidth="true"/>
+    <col min="16" max="16" width="15.625" style="8" bestFit="true" customWidth="true"/>
+    <col min="17" max="17" width="11.625" style="8" bestFit="true" customWidth="true"/>
+    <col min="18" max="26" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1579,6 +1598,68 @@
       <c r="Q17" s="4">
         <v>1300</v>
       </c>
+    </row>
+    <row r="18" spans="1:26" ht="15" customHeight="true">
+      <c r="A18" s="6">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2</v>
+      </c>
+      <c r="E18" s="6">
+        <v>50</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="6">
+        <v>5</v>
+      </c>
+      <c r="I18" s="6">
+        <v>90</v>
+      </c>
+      <c r="J18" s="6">
+        <v>50</v>
+      </c>
+      <c r="K18" s="6">
+        <v>7</v>
+      </c>
+      <c r="L18" s="6">
+        <v>20</v>
+      </c>
+      <c r="M18" s="6">
+        <v>6</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0</v>
+      </c>
+      <c r="P18" s="6">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>1500</v>
+      </c>
+      <c r="R18" s="7" t="s"/>
+      <c r="S18" s="7" t="s"/>
+      <c r="T18" s="7" t="s"/>
+      <c r="U18" s="7" t="s"/>
+      <c r="V18" s="7" t="s"/>
+      <c r="W18" s="7" t="s"/>
+      <c r="X18" s="7" t="s"/>
+      <c r="Y18" s="7" t="s"/>
+      <c r="Z18" s="7" t="s"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
